--- a/ONCHO/Entomological survey Survey/Nigeria/2025/ng_oncho_2503_2_river_inspection_tar.xlsx
+++ b/ONCHO/Entomological survey Survey/Nigeria/2025/ng_oncho_2503_2_river_inspection_tar.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\ONCHO\Entomological survey Survey\Nigeria\2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EE06810-D79E-493D-A702-C3BC9F557850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA800EAF-A8F1-46A9-8FDE-2ACF6D2C2B25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -535,9 +535,6 @@
     <t>ng_oncho_2503_2_river_inspection_tar</t>
   </si>
   <si>
-    <t>(Taraba) 2. River inspection Form</t>
-  </si>
-  <si>
     <t>TARABA</t>
   </si>
   <si>
@@ -926,6 +923,9 @@
   </si>
   <si>
     <t>TAR_SAR_N_053</t>
+  </si>
+  <si>
+    <t>(Taraba) 2. River inspection Form V4</t>
   </si>
 </sst>
 </file>
@@ -1120,17 +1120,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2618,10 +2608,10 @@
         <v>107</v>
       </c>
       <c r="B32" s="21" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -2633,13 +2623,13 @@
         <v>106</v>
       </c>
       <c r="B34" s="21" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D34" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -2647,13 +2637,13 @@
         <v>106</v>
       </c>
       <c r="B35" s="21" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D35" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -2661,13 +2651,13 @@
         <v>106</v>
       </c>
       <c r="B36" s="21" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -2675,13 +2665,13 @@
         <v>106</v>
       </c>
       <c r="B37" s="21" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D37" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -2689,13 +2679,13 @@
         <v>106</v>
       </c>
       <c r="B38" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -2703,13 +2693,13 @@
         <v>106</v>
       </c>
       <c r="B39" s="21" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D39" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -2717,13 +2707,13 @@
         <v>106</v>
       </c>
       <c r="B40" s="21" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D40" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -2731,13 +2721,13 @@
         <v>106</v>
       </c>
       <c r="B41" s="21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D41" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -2745,13 +2735,13 @@
         <v>106</v>
       </c>
       <c r="B42" s="21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D42" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -2759,13 +2749,13 @@
         <v>106</v>
       </c>
       <c r="B43" s="21" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D43" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -2773,13 +2763,13 @@
         <v>106</v>
       </c>
       <c r="B44" s="21" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D44" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -2787,13 +2777,13 @@
         <v>106</v>
       </c>
       <c r="B45" s="21" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D45" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -2801,13 +2791,13 @@
         <v>106</v>
       </c>
       <c r="B46" s="21" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C46" s="21" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D46" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -2815,13 +2805,13 @@
         <v>106</v>
       </c>
       <c r="B47" s="21" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C47" s="21" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D47" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -2834,13 +2824,13 @@
         <v>155</v>
       </c>
       <c r="B49" s="21" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C49" s="21" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E49" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -2848,13 +2838,13 @@
         <v>155</v>
       </c>
       <c r="B50" s="21" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C50" s="21" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E50" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -2862,13 +2852,13 @@
         <v>155</v>
       </c>
       <c r="B51" s="21" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C51" s="21" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E51" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -2876,13 +2866,13 @@
         <v>155</v>
       </c>
       <c r="B52" s="21" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C52" s="21" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E52" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -2890,13 +2880,13 @@
         <v>155</v>
       </c>
       <c r="B53" s="21" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C53" s="21" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E53" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -2904,13 +2894,13 @@
         <v>155</v>
       </c>
       <c r="B54" s="21" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C54" s="21" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E54" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -2918,13 +2908,13 @@
         <v>155</v>
       </c>
       <c r="B55" s="21" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C55" s="21" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E55" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -2932,13 +2922,13 @@
         <v>155</v>
       </c>
       <c r="B56" s="21" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C56" s="21" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E56" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -2946,13 +2936,13 @@
         <v>155</v>
       </c>
       <c r="B57" s="21" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C57" s="21" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E57" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -2960,13 +2950,13 @@
         <v>155</v>
       </c>
       <c r="B58" s="21" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C58" s="21" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E58" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -2974,13 +2964,13 @@
         <v>155</v>
       </c>
       <c r="B59" s="21" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C59" s="21" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E59" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -2988,13 +2978,13 @@
         <v>155</v>
       </c>
       <c r="B60" s="21" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C60" s="21" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E60" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -3002,13 +2992,13 @@
         <v>155</v>
       </c>
       <c r="B61" s="21" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C61" s="21" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E61" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -3016,13 +3006,13 @@
         <v>155</v>
       </c>
       <c r="B62" s="21" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C62" s="21" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E62" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -3030,13 +3020,13 @@
         <v>155</v>
       </c>
       <c r="B63" s="21" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C63" s="21" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E63" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -3044,13 +3034,13 @@
         <v>155</v>
       </c>
       <c r="B64" s="21" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C64" s="21" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E64" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -3058,13 +3048,13 @@
         <v>155</v>
       </c>
       <c r="B65" s="21" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C65" s="21" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E65" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -3072,13 +3062,13 @@
         <v>155</v>
       </c>
       <c r="B66" s="21" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C66" s="21" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E66" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -3086,13 +3076,13 @@
         <v>155</v>
       </c>
       <c r="B67" s="21" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C67" s="21" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E67" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
@@ -3100,13 +3090,13 @@
         <v>155</v>
       </c>
       <c r="B68" s="21" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C68" s="21" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E68" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -3114,13 +3104,13 @@
         <v>155</v>
       </c>
       <c r="B69" s="21" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C69" s="21" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E69" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
@@ -3128,13 +3118,13 @@
         <v>155</v>
       </c>
       <c r="B70" s="21" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C70" s="21" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E70" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -3142,13 +3132,13 @@
         <v>155</v>
       </c>
       <c r="B71" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C71" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E71" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -3156,13 +3146,13 @@
         <v>155</v>
       </c>
       <c r="B72" s="21" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C72" s="21" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E72" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -3170,13 +3160,13 @@
         <v>155</v>
       </c>
       <c r="B73" s="21" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C73" s="21" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E73" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -3184,13 +3174,13 @@
         <v>155</v>
       </c>
       <c r="B74" s="21" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C74" s="21" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E74" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
@@ -3198,13 +3188,13 @@
         <v>155</v>
       </c>
       <c r="B75" s="21" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C75" s="21" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E75" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -3212,13 +3202,13 @@
         <v>155</v>
       </c>
       <c r="B76" s="21" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C76" s="21" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E76" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -3226,13 +3216,13 @@
         <v>155</v>
       </c>
       <c r="B77" s="21" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C77" s="21" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E77" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
@@ -3240,13 +3230,13 @@
         <v>155</v>
       </c>
       <c r="B78" s="21" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C78" s="21" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E78" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -3254,13 +3244,13 @@
         <v>155</v>
       </c>
       <c r="B79" s="21" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C79" s="21" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E79" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -3268,13 +3258,13 @@
         <v>155</v>
       </c>
       <c r="B80" s="21" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C80" s="21" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E80" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -3282,13 +3272,13 @@
         <v>155</v>
       </c>
       <c r="B81" s="21" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C81" s="21" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E81" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -3296,13 +3286,13 @@
         <v>155</v>
       </c>
       <c r="B82" s="21" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C82" s="21" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E82" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
@@ -3310,13 +3300,13 @@
         <v>155</v>
       </c>
       <c r="B83" s="21" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C83" s="21" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E83" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -3324,13 +3314,13 @@
         <v>155</v>
       </c>
       <c r="B84" s="21" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C84" s="21" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E84" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -3338,13 +3328,13 @@
         <v>155</v>
       </c>
       <c r="B85" s="21" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C85" s="21" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E85" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -3352,13 +3342,13 @@
         <v>155</v>
       </c>
       <c r="B86" s="21" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C86" s="21" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E86" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -3366,13 +3356,13 @@
         <v>155</v>
       </c>
       <c r="B87" s="21" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C87" s="21" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E87" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -3380,13 +3370,13 @@
         <v>155</v>
       </c>
       <c r="B88" s="21" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C88" s="21" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E88" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -3394,13 +3384,13 @@
         <v>155</v>
       </c>
       <c r="B89" s="21" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C89" s="21" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E89" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -3408,13 +3398,13 @@
         <v>155</v>
       </c>
       <c r="B90" s="21" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C90" s="21" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E90" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -3422,13 +3412,13 @@
         <v>155</v>
       </c>
       <c r="B91" s="21" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C91" s="21" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E91" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -3436,13 +3426,13 @@
         <v>155</v>
       </c>
       <c r="B92" s="21" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C92" s="21" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E92" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -3450,13 +3440,13 @@
         <v>155</v>
       </c>
       <c r="B93" s="21" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C93" s="21" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E93" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
@@ -3464,13 +3454,13 @@
         <v>155</v>
       </c>
       <c r="B94" s="21" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C94" s="21" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E94" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
@@ -3478,13 +3468,13 @@
         <v>155</v>
       </c>
       <c r="B95" s="21" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C95" s="21" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E95" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -3492,13 +3482,13 @@
         <v>155</v>
       </c>
       <c r="B96" s="21" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C96" s="21" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E96" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3506,13 +3496,13 @@
         <v>155</v>
       </c>
       <c r="B97" s="21" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C97" s="21" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E97" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3520,13 +3510,13 @@
         <v>155</v>
       </c>
       <c r="B98" s="21" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C98" s="21" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E98" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3534,13 +3524,13 @@
         <v>155</v>
       </c>
       <c r="B99" s="21" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C99" s="21" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E99" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3548,13 +3538,13 @@
         <v>155</v>
       </c>
       <c r="B100" s="21" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C100" s="21" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E100" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3562,13 +3552,13 @@
         <v>155</v>
       </c>
       <c r="B101" s="21" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C101" s="21" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E101" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3576,13 +3566,13 @@
         <v>155</v>
       </c>
       <c r="B102" s="21" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C102" s="21" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E102" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -3590,13 +3580,13 @@
         <v>155</v>
       </c>
       <c r="B103" s="21" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C103" s="21" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E103" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -3604,13 +3594,13 @@
         <v>155</v>
       </c>
       <c r="B104" s="21" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C104" s="21" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E104" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -3618,13 +3608,13 @@
         <v>155</v>
       </c>
       <c r="B105" s="21" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C105" s="21" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E105" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3632,13 +3622,13 @@
         <v>155</v>
       </c>
       <c r="B106" s="21" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C106" s="21" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E106" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3650,13 +3640,13 @@
         <v>38</v>
       </c>
       <c r="B108" s="21" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C108" s="21" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F108" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3664,13 +3654,13 @@
         <v>38</v>
       </c>
       <c r="B109" s="21" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C109" s="21" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F109" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -3678,13 +3668,13 @@
         <v>38</v>
       </c>
       <c r="B110" s="21" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C110" s="21" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F110" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -3692,13 +3682,13 @@
         <v>38</v>
       </c>
       <c r="B111" s="21" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C111" s="21" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F111" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -3706,13 +3696,13 @@
         <v>38</v>
       </c>
       <c r="B112" s="21" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C112" s="21" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F112" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -3720,13 +3710,13 @@
         <v>38</v>
       </c>
       <c r="B113" s="21" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C113" s="21" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F113" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -3734,13 +3724,13 @@
         <v>38</v>
       </c>
       <c r="B114" s="21" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C114" s="21" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F114" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -3748,13 +3738,13 @@
         <v>38</v>
       </c>
       <c r="B115" s="21" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C115" s="21" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F115" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -3762,13 +3752,13 @@
         <v>38</v>
       </c>
       <c r="B116" s="21" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C116" s="21" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F116" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -3776,13 +3766,13 @@
         <v>38</v>
       </c>
       <c r="B117" s="21" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C117" s="21" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F117" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -3790,13 +3780,13 @@
         <v>38</v>
       </c>
       <c r="B118" s="21" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C118" s="21" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F118" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -3804,13 +3794,13 @@
         <v>38</v>
       </c>
       <c r="B119" s="21" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C119" s="21" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F119" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -3818,13 +3808,13 @@
         <v>38</v>
       </c>
       <c r="B120" s="21" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C120" s="21" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F120" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -3832,13 +3822,13 @@
         <v>38</v>
       </c>
       <c r="B121" s="21" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C121" s="21" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F121" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -3846,13 +3836,13 @@
         <v>38</v>
       </c>
       <c r="B122" s="21" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C122" s="21" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F122" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -3860,13 +3850,13 @@
         <v>38</v>
       </c>
       <c r="B123" s="21" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C123" s="21" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F123" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -3874,13 +3864,13 @@
         <v>38</v>
       </c>
       <c r="B124" s="21" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C124" s="21" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F124" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -3888,13 +3878,13 @@
         <v>38</v>
       </c>
       <c r="B125" s="21" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C125" s="21" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F125" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -3902,13 +3892,13 @@
         <v>38</v>
       </c>
       <c r="B126" s="21" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C126" s="21" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F126" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -3916,13 +3906,13 @@
         <v>38</v>
       </c>
       <c r="B127" s="21" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C127" s="21" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F127" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -3930,13 +3920,13 @@
         <v>38</v>
       </c>
       <c r="B128" s="21" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C128" s="21" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F128" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -3944,13 +3934,13 @@
         <v>38</v>
       </c>
       <c r="B129" s="21" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C129" s="21" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F129" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -3958,13 +3948,13 @@
         <v>38</v>
       </c>
       <c r="B130" s="21" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C130" s="21" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F130" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -3972,13 +3962,13 @@
         <v>38</v>
       </c>
       <c r="B131" s="21" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C131" s="21" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F131" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -3986,13 +3976,13 @@
         <v>38</v>
       </c>
       <c r="B132" s="21" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C132" s="21" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F132" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4000,13 +3990,13 @@
         <v>38</v>
       </c>
       <c r="B133" s="21" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C133" s="21" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F133" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4014,13 +4004,13 @@
         <v>38</v>
       </c>
       <c r="B134" s="21" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C134" s="21" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F134" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4028,13 +4018,13 @@
         <v>38</v>
       </c>
       <c r="B135" s="21" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C135" s="21" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F135" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4042,13 +4032,13 @@
         <v>38</v>
       </c>
       <c r="B136" s="21" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C136" s="21" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F136" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -4056,13 +4046,13 @@
         <v>38</v>
       </c>
       <c r="B137" s="21" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C137" s="21" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F137" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -4070,13 +4060,13 @@
         <v>38</v>
       </c>
       <c r="B138" s="21" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C138" s="21" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F138" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -4084,13 +4074,13 @@
         <v>38</v>
       </c>
       <c r="B139" s="21" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C139" s="21" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F139" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -4098,13 +4088,13 @@
         <v>38</v>
       </c>
       <c r="B140" s="21" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C140" s="21" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F140" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -4112,13 +4102,13 @@
         <v>38</v>
       </c>
       <c r="B141" s="21" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C141" s="21" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F141" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -4126,13 +4116,13 @@
         <v>38</v>
       </c>
       <c r="B142" s="21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C142" s="21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F142" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -4140,13 +4130,13 @@
         <v>38</v>
       </c>
       <c r="B143" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C143" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F143" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -4154,13 +4144,13 @@
         <v>38</v>
       </c>
       <c r="B144" s="21" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C144" s="21" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F144" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -4168,13 +4158,13 @@
         <v>38</v>
       </c>
       <c r="B145" s="21" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C145" s="21" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F145" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -4182,13 +4172,13 @@
         <v>38</v>
       </c>
       <c r="B146" s="21" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C146" s="21" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F146" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -4196,13 +4186,13 @@
         <v>38</v>
       </c>
       <c r="B147" s="21" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C147" s="21" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F147" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -4210,13 +4200,13 @@
         <v>38</v>
       </c>
       <c r="B148" s="21" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C148" s="21" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F148" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -4224,13 +4214,13 @@
         <v>38</v>
       </c>
       <c r="B149" s="21" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C149" s="21" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F149" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -4238,13 +4228,13 @@
         <v>38</v>
       </c>
       <c r="B150" s="21" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C150" s="21" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F150" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -4252,13 +4242,13 @@
         <v>38</v>
       </c>
       <c r="B151" s="21" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C151" s="21" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F151" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -4266,13 +4256,13 @@
         <v>38</v>
       </c>
       <c r="B152" s="21" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C152" s="21" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F152" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -4280,13 +4270,13 @@
         <v>38</v>
       </c>
       <c r="B153" s="21" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C153" s="21" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F153" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -4294,13 +4284,13 @@
         <v>38</v>
       </c>
       <c r="B154" s="21" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C154" s="21" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F154" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -4308,13 +4298,13 @@
         <v>38</v>
       </c>
       <c r="B155" s="21" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C155" s="21" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F155" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -4322,13 +4312,13 @@
         <v>38</v>
       </c>
       <c r="B156" s="21" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C156" s="21" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F156" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -4336,13 +4326,13 @@
         <v>38</v>
       </c>
       <c r="B157" s="21" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C157" s="21" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F157" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -4350,13 +4340,13 @@
         <v>38</v>
       </c>
       <c r="B158" s="21" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C158" s="21" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F158" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -4364,13 +4354,13 @@
         <v>38</v>
       </c>
       <c r="B159" s="21" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C159" s="21" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F159" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -4378,13 +4368,13 @@
         <v>38</v>
       </c>
       <c r="B160" s="21" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C160" s="21" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F160" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -4392,13 +4382,13 @@
         <v>38</v>
       </c>
       <c r="B161" s="21" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C161" s="21" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F161" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -4406,13 +4396,13 @@
         <v>38</v>
       </c>
       <c r="B162" s="21" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C162" s="21" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F162" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -4420,13 +4410,13 @@
         <v>38</v>
       </c>
       <c r="B163" s="21" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C163" s="21" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F163" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -4434,13 +4424,13 @@
         <v>38</v>
       </c>
       <c r="B164" s="21" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C164" s="21" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F164" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -4448,13 +4438,13 @@
         <v>38</v>
       </c>
       <c r="B165" s="21" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C165" s="21" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F165" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>
@@ -4490,7 +4480,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>164</v>
+        <v>294</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>163</v>
